--- a/data/NISR_SDG_Automation_Mapping_Built.xlsx
+++ b/data/NISR_SDG_Automation_Mapping_Built.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kpier\OneDrive\Documents\GitHub\sdg-data-rwanda\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA63285-9CDA-4603-A70E-175AAB892AA6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA2F113-076A-471E-8DCA-2493C99A15D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3261" uniqueCount="1278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3261" uniqueCount="1279">
   <si>
     <t>Indicator</t>
   </si>
@@ -2459,9 +2459,6 @@
     <t>p. 79</t>
   </si>
   <si>
-    <t>Table 9.1</t>
-  </si>
-  <si>
     <t>Headcount poverty rate (%)—EICV7 (2023/24)</t>
   </si>
   <si>
@@ -3885,6 +3882,12 @@
   </si>
   <si>
     <t>Table 5.1, Headcount poverty rate (%)—EICV7 (2023/24), p. 79, EICV7 Main Indicators Report 2023/24 (2025)</t>
+  </si>
+  <si>
+    <t>Table 5.1</t>
+  </si>
+  <si>
+    <t>EICV7 Poverty Thematic Report</t>
   </si>
 </sst>
 </file>
@@ -3896,7 +3899,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4359,7 +4362,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AU128"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
     <col min="2" max="2" width="82.88671875" customWidth="1"/>
@@ -4393,7 +4396,7 @@
     <col min="47" max="47" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="15.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:47" ht="15.9" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -4536,7 +4539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>22</v>
       </c>
@@ -4623,7 +4626,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:47" ht="26.4" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>31</v>
       </c>
@@ -4709,10 +4712,10 @@
         <v>27.4</v>
       </c>
       <c r="AU3" s="8" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="4" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="4" spans="1:47" ht="26.4" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>36</v>
       </c>
@@ -4805,7 +4808,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>43</v>
       </c>
@@ -4888,7 +4891,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>49</v>
       </c>
@@ -4967,7 +4970,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>54</v>
       </c>
@@ -5046,7 +5049,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>61</v>
       </c>
@@ -5141,7 +5144,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>68</v>
       </c>
@@ -5232,7 +5235,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>72</v>
       </c>
@@ -5323,7 +5326,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>78</v>
       </c>
@@ -5406,7 +5409,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>84</v>
       </c>
@@ -5487,7 +5490,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:47" ht="26.4" customHeight="1">
       <c r="A13" s="8" t="s">
         <v>89</v>
       </c>
@@ -5578,7 +5581,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:47" ht="26.4" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>95</v>
       </c>
@@ -5667,7 +5670,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:47" ht="39.6" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>101</v>
       </c>
@@ -5754,7 +5757,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:47" ht="39.6" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>107</v>
       </c>
@@ -5843,7 +5846,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>114</v>
       </c>
@@ -5926,7 +5929,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:47" ht="39.6" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>120</v>
       </c>
@@ -6015,7 +6018,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:47" ht="39.6" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>125</v>
       </c>
@@ -6104,7 +6107,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:47" ht="39.6" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>129</v>
       </c>
@@ -6197,7 +6200,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="21" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:47" ht="39.6" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>134</v>
       </c>
@@ -6288,7 +6291,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="22" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>139</v>
       </c>
@@ -6369,7 +6372,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="23" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A23" s="8" t="s">
         <v>146</v>
       </c>
@@ -6460,7 +6463,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="24" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>152</v>
       </c>
@@ -6547,7 +6550,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="25" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>159</v>
       </c>
@@ -6630,7 +6633,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="26" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>164</v>
       </c>
@@ -6723,7 +6726,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="27" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>169</v>
       </c>
@@ -6804,7 +6807,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="28" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:47" ht="26.4" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>175</v>
       </c>
@@ -6905,7 +6908,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="29" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:47" ht="39.6" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>180</v>
       </c>
@@ -6994,7 +6997,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="30" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:47" ht="39.6" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>189</v>
       </c>
@@ -7081,7 +7084,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="31" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A31" s="8" t="s">
         <v>196</v>
       </c>
@@ -7164,7 +7167,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="32" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A32" s="8" t="s">
         <v>202</v>
       </c>
@@ -7245,7 +7248,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="33" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:47" ht="26.4" customHeight="1">
       <c r="A33" s="8" t="s">
         <v>208</v>
       </c>
@@ -7328,7 +7331,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="34" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A34" s="8" t="s">
         <v>215</v>
       </c>
@@ -7421,7 +7424,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="35" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A35" s="8" t="s">
         <v>223</v>
       </c>
@@ -7502,7 +7505,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="36" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A36" s="8" t="s">
         <v>231</v>
       </c>
@@ -7583,7 +7586,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="37" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A37" s="8" t="s">
         <v>238</v>
       </c>
@@ -7664,7 +7667,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="38" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:47" ht="39.6" customHeight="1">
       <c r="A38" s="8" t="s">
         <v>246</v>
       </c>
@@ -7749,7 +7752,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="39" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A39" s="8" t="s">
         <v>256</v>
       </c>
@@ -7834,7 +7837,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="40" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A40" s="8" t="s">
         <v>262</v>
       </c>
@@ -7923,7 +7926,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="41" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:47" ht="26.4" customHeight="1">
       <c r="A41" s="8" t="s">
         <v>270</v>
       </c>
@@ -8006,7 +8009,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="42" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:47" ht="26.4" customHeight="1">
       <c r="A42" s="8" t="s">
         <v>275</v>
       </c>
@@ -8089,7 +8092,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="43" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A43" s="8" t="s">
         <v>282</v>
       </c>
@@ -8168,7 +8171,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="44" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A44" s="8" t="s">
         <v>288</v>
       </c>
@@ -8259,7 +8262,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="45" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A45" s="8" t="s">
         <v>296</v>
       </c>
@@ -8352,7 +8355,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="46" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:47" ht="26.4" customHeight="1">
       <c r="A46" s="8" t="s">
         <v>300</v>
       </c>
@@ -8435,7 +8438,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="47" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:47" ht="39.6" customHeight="1">
       <c r="A47" s="8" t="s">
         <v>305</v>
       </c>
@@ -8516,7 +8519,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="48" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:47" ht="26.4" customHeight="1">
       <c r="A48" s="8" t="s">
         <v>310</v>
       </c>
@@ -8601,7 +8604,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="49" spans="1:47" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:47" ht="52.8" customHeight="1">
       <c r="A49" s="8" t="s">
         <v>317</v>
       </c>
@@ -8692,7 +8695,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="50" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A50" s="8" t="s">
         <v>323</v>
       </c>
@@ -8789,7 +8792,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="51" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:47" ht="39.6" customHeight="1">
       <c r="A51" s="8" t="s">
         <v>330</v>
       </c>
@@ -8882,7 +8885,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="52" spans="1:47" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:47" ht="52.8" customHeight="1">
       <c r="A52" s="8" t="s">
         <v>335</v>
       </c>
@@ -8963,7 +8966,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="53" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A53" s="8" t="s">
         <v>340</v>
       </c>
@@ -9044,7 +9047,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="54" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A54" s="8" t="s">
         <v>346</v>
       </c>
@@ -9129,7 +9132,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="55" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A55" s="8" t="s">
         <v>352</v>
       </c>
@@ -9214,7 +9217,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="56" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A56" s="8" t="s">
         <v>358</v>
       </c>
@@ -9299,7 +9302,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="57" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A57" s="8" t="s">
         <v>362</v>
       </c>
@@ -9382,7 +9385,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="58" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A58" s="8" t="s">
         <v>368</v>
       </c>
@@ -9461,7 +9464,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="59" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A59" s="8" t="s">
         <v>373</v>
       </c>
@@ -9542,7 +9545,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="60" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A60" s="8" t="s">
         <v>376</v>
       </c>
@@ -9623,7 +9626,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="61" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A61" s="8" t="s">
         <v>380</v>
       </c>
@@ -9702,7 +9705,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="62" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A62" s="8" t="s">
         <v>384</v>
       </c>
@@ -9781,7 +9784,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="63" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A63" s="8" t="s">
         <v>390</v>
       </c>
@@ -9888,7 +9891,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="64" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A64" s="8" t="s">
         <v>395</v>
       </c>
@@ -9977,7 +9980,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="65" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:47" ht="26.4" customHeight="1">
       <c r="A65" s="8" t="s">
         <v>399</v>
       </c>
@@ -10060,7 +10063,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="66" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A66" s="8" t="s">
         <v>404</v>
       </c>
@@ -10143,7 +10146,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="67" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A67" s="8" t="s">
         <v>410</v>
       </c>
@@ -10224,7 +10227,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="68" spans="1:47" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:47" ht="52.8" customHeight="1">
       <c r="A68" s="8" t="s">
         <v>414</v>
       </c>
@@ -10349,7 +10352,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="69" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A69" s="8" t="s">
         <v>419</v>
       </c>
@@ -10438,7 +10441,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="70" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:47" ht="26.4" customHeight="1">
       <c r="A70" s="8" t="s">
         <v>424</v>
       </c>
@@ -10531,7 +10534,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="71" spans="1:47" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:47" ht="52.8" customHeight="1">
       <c r="A71" s="8" t="s">
         <v>429</v>
       </c>
@@ -10624,7 +10627,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="72" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:47" ht="26.4" customHeight="1">
       <c r="A72" s="8" t="s">
         <v>436</v>
       </c>
@@ -10719,7 +10722,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="73" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:47" ht="26.4" customHeight="1">
       <c r="A73" s="8" t="s">
         <v>441</v>
       </c>
@@ -10812,7 +10815,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="74" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:47" ht="39.6" customHeight="1">
       <c r="A74" s="8" t="s">
         <v>448</v>
       </c>
@@ -10897,7 +10900,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="75" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A75" s="8" t="s">
         <v>455</v>
       </c>
@@ -10978,7 +10981,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="76" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A76" s="8" t="s">
         <v>461</v>
       </c>
@@ -11069,7 +11072,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="77" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A77" s="8" t="s">
         <v>468</v>
       </c>
@@ -11154,7 +11157,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="78" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A78" s="8" t="s">
         <v>474</v>
       </c>
@@ -11249,7 +11252,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="79" spans="1:47" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:47" ht="52.8" customHeight="1">
       <c r="A79" s="8" t="s">
         <v>480</v>
       </c>
@@ -11336,7 +11339,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="80" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A80" s="8" t="s">
         <v>485</v>
       </c>
@@ -11417,7 +11420,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="81" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A81" s="8" t="s">
         <v>492</v>
       </c>
@@ -11510,7 +11513,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="82" spans="1:47" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:47" ht="52.8" customHeight="1">
       <c r="A82" s="8" t="s">
         <v>499</v>
       </c>
@@ -11635,7 +11638,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="83" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:47" ht="26.4" customHeight="1">
       <c r="A83" s="8" t="s">
         <v>504</v>
       </c>
@@ -11728,7 +11731,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="84" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A84" s="8" t="s">
         <v>508</v>
       </c>
@@ -11847,7 +11850,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="85" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A85" s="8" t="s">
         <v>515</v>
       </c>
@@ -11930,7 +11933,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="86" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A86" s="8" t="s">
         <v>521</v>
       </c>
@@ -12017,7 +12020,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="87" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A87" s="8" t="s">
         <v>525</v>
       </c>
@@ -12106,7 +12109,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="88" spans="1:47" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:47" ht="52.8" customHeight="1">
       <c r="A88" s="8" t="s">
         <v>531</v>
       </c>
@@ -12191,7 +12194,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="89" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A89" s="8" t="s">
         <v>536</v>
       </c>
@@ -12286,7 +12289,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="90" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A90" s="8" t="s">
         <v>540</v>
       </c>
@@ -12377,7 +12380,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="91" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A91" s="8" t="s">
         <v>546</v>
       </c>
@@ -12460,7 +12463,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="92" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:47" ht="39.6" customHeight="1">
       <c r="A92" s="8" t="s">
         <v>551</v>
       </c>
@@ -12547,7 +12550,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="93" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A93" s="8" t="s">
         <v>559</v>
       </c>
@@ -12642,7 +12645,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="94" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A94" s="8" t="s">
         <v>563</v>
       </c>
@@ -12733,7 +12736,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="95" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A95" s="8" t="s">
         <v>565</v>
       </c>
@@ -12824,7 +12827,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="96" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A96" s="8" t="s">
         <v>567</v>
       </c>
@@ -12919,7 +12922,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="97" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A97" s="8" t="s">
         <v>569</v>
       </c>
@@ -13010,7 +13013,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="98" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A98" s="8" t="s">
         <v>571</v>
       </c>
@@ -13091,7 +13094,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="99" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A99" s="8" t="s">
         <v>577</v>
       </c>
@@ -13174,7 +13177,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="100" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A100" s="8" t="s">
         <v>583</v>
       </c>
@@ -13257,7 +13260,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="101" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A101" s="8" t="s">
         <v>589</v>
       </c>
@@ -13338,7 +13341,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="102" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A102" s="8" t="s">
         <v>595</v>
       </c>
@@ -13425,7 +13428,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="103" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A103" s="8" t="s">
         <v>599</v>
       </c>
@@ -13518,7 +13521,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="104" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:47" ht="39.6" customHeight="1">
       <c r="A104" s="8" t="s">
         <v>605</v>
       </c>
@@ -13601,7 +13604,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="105" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A105" s="8" t="s">
         <v>612</v>
       </c>
@@ -13696,7 +13699,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="106" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A106" s="8" t="s">
         <v>616</v>
       </c>
@@ -13783,7 +13786,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="107" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A107" s="8" t="s">
         <v>620</v>
       </c>
@@ -13874,7 +13877,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="108" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A108" s="8" t="s">
         <v>626</v>
       </c>
@@ -13957,7 +13960,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="109" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A109" s="8" t="s">
         <v>629</v>
       </c>
@@ -14040,7 +14043,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="110" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A110" s="8" t="s">
         <v>632</v>
       </c>
@@ -14133,7 +14136,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="111" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A111" s="8" t="s">
         <v>638</v>
       </c>
@@ -14230,7 +14233,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="112" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A112" s="8" t="s">
         <v>642</v>
       </c>
@@ -14317,7 +14320,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="113" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A113" s="8" t="s">
         <v>646</v>
       </c>
@@ -14400,7 +14403,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="114" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A114" s="8" t="s">
         <v>652</v>
       </c>
@@ -14499,7 +14502,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="115" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A115" s="8" t="s">
         <v>656</v>
       </c>
@@ -14598,7 +14601,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="116" spans="1:47" ht="26.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:47" ht="26.4" hidden="1" customHeight="1">
       <c r="A116" s="8" t="s">
         <v>660</v>
       </c>
@@ -14683,7 +14686,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="117" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:47" ht="39.6" customHeight="1">
       <c r="A117" s="8" t="s">
         <v>666</v>
       </c>
@@ -14768,7 +14771,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="118" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A118" s="8" t="s">
         <v>669</v>
       </c>
@@ -14861,7 +14864,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="119" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A119" s="8" t="s">
         <v>675</v>
       </c>
@@ -14952,7 +14955,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="120" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A120" s="8" t="s">
         <v>678</v>
       </c>
@@ -15037,7 +15040,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="121" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A121" s="8" t="s">
         <v>682</v>
       </c>
@@ -15132,7 +15135,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="122" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A122" s="8" t="s">
         <v>685</v>
       </c>
@@ -15227,7 +15230,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="123" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A123" s="8" t="s">
         <v>689</v>
       </c>
@@ -15316,7 +15319,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="124" spans="1:47" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:47" ht="26.4" customHeight="1">
       <c r="A124" s="8" t="s">
         <v>696</v>
       </c>
@@ -15399,7 +15402,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="125" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A125" s="8" t="s">
         <v>701</v>
       </c>
@@ -15484,7 +15487,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="126" spans="1:47" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:47" ht="39.6" customHeight="1">
       <c r="A126" s="8" t="s">
         <v>705</v>
       </c>
@@ -15605,7 +15608,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="127" spans="1:47" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:47" ht="52.8" customHeight="1">
       <c r="A127" s="8" t="s">
         <v>709</v>
       </c>
@@ -15692,7 +15695,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="128" spans="1:47" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:47" ht="14.4" hidden="1" customHeight="1">
       <c r="A128" s="8" t="s">
         <v>715</v>
       </c>
@@ -15797,7 +15800,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="28.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.6640625" style="1" customWidth="1"/>
@@ -15808,7 +15811,7 @@
     <col min="8" max="16384" width="9.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>721</v>
       </c>
@@ -15829,7 +15832,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>727</v>
       </c>
@@ -15849,7 +15852,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>732</v>
       </c>
@@ -15863,7 +15866,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
         <v>734</v>
       </c>
@@ -15877,7 +15880,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
         <v>737</v>
       </c>
@@ -15891,7 +15894,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
         <v>739</v>
       </c>
@@ -15905,7 +15908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>741</v>
       </c>
@@ -15919,7 +15922,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7">
       <c r="A8" s="1" t="s">
         <v>742</v>
       </c>
@@ -15933,7 +15936,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7">
       <c r="A9" s="1" t="s">
         <v>743</v>
       </c>
@@ -15947,7 +15950,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="A10" s="1" t="s">
         <v>745</v>
       </c>
@@ -15961,7 +15964,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="A11" s="1" t="s">
         <v>746</v>
       </c>
@@ -15975,7 +15978,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="A12" s="1" t="s">
         <v>747</v>
       </c>
@@ -15989,7 +15992,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="A13" s="1" t="s">
         <v>749</v>
       </c>
@@ -16003,7 +16006,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="A14" s="1" t="s">
         <v>750</v>
       </c>
@@ -16017,7 +16020,7 @@
         <v>751</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="A15" s="1" t="s">
         <v>752</v>
       </c>
@@ -16031,7 +16034,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="A16" s="1" t="s">
         <v>753</v>
       </c>
@@ -16045,7 +16048,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4">
       <c r="A17" s="1" t="s">
         <v>754</v>
       </c>
@@ -16059,7 +16062,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4">
       <c r="A18" s="1" t="s">
         <v>755</v>
       </c>
@@ -16073,7 +16076,7 @@
         <v>757</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4">
       <c r="A19" s="1" t="s">
         <v>758</v>
       </c>
@@ -16087,7 +16090,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4">
       <c r="A20" s="1" t="s">
         <v>760</v>
       </c>
@@ -16101,7 +16104,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4">
       <c r="A21" s="1" t="s">
         <v>762</v>
       </c>
@@ -16115,7 +16118,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4">
       <c r="A22" s="1" t="s">
         <v>764</v>
       </c>
@@ -16129,7 +16132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4">
       <c r="A23" s="1" t="s">
         <v>765</v>
       </c>
@@ -16143,7 +16146,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4">
       <c r="A24" s="1" t="s">
         <v>766</v>
       </c>
@@ -16165,7 +16168,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AG41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
@@ -16186,7 +16189,7 @@
     <col min="32" max="33" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" ht="28.8">
       <c r="A1" s="7" t="s">
         <v>767</v>
       </c>
@@ -16287,7 +16290,7 @@
         <v>795</v>
       </c>
     </row>
-    <row r="2" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" ht="39.6" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>796</v>
       </c>
@@ -16319,7 +16322,7 @@
         <v>797</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>798</v>
+        <v>1278</v>
       </c>
       <c r="L2" s="8">
         <v>2025</v>
@@ -16334,46 +16337,46 @@
         <v>801</v>
       </c>
       <c r="P2" s="8" t="s">
+        <v>1277</v>
+      </c>
+      <c r="Q2" s="8" t="s">
         <v>802</v>
       </c>
-      <c r="Q2" s="8" t="s">
+      <c r="R2" s="8" t="s">
         <v>803</v>
       </c>
-      <c r="R2" s="8" t="s">
+      <c r="S2" s="8" t="s">
         <v>804</v>
       </c>
-      <c r="S2" s="8" t="s">
+      <c r="T2" s="8" t="s">
         <v>805</v>
       </c>
-      <c r="T2" s="8" t="s">
+      <c r="U2" s="8" t="s">
         <v>806</v>
       </c>
-      <c r="U2" s="8" t="s">
+      <c r="V2" s="8" t="s">
         <v>807</v>
       </c>
-      <c r="V2" s="8" t="s">
+      <c r="W2" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="W2" s="8" t="s">
+      <c r="X2" s="8" t="s">
         <v>809</v>
       </c>
-      <c r="X2" s="8" t="s">
+      <c r="Y2" s="8" t="s">
         <v>810</v>
       </c>
-      <c r="Y2" s="8" t="s">
+      <c r="Z2" s="8" t="s">
         <v>811</v>
       </c>
-      <c r="Z2" s="8" t="s">
+      <c r="AA2" s="8" t="s">
         <v>812</v>
       </c>
-      <c r="AA2" s="8" t="s">
+      <c r="AB2" s="8" t="s">
         <v>813</v>
       </c>
-      <c r="AB2" s="8" t="s">
+      <c r="AC2" s="8" t="s">
         <v>814</v>
-      </c>
-      <c r="AC2" s="8" t="s">
-        <v>815</v>
       </c>
       <c r="AD2" s="8">
         <v>2025</v>
@@ -16382,27 +16385,27 @@
         <v>2024</v>
       </c>
       <c r="AF2" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="AG2" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="AG2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:33" ht="66" customHeight="1">
+      <c r="A3" s="8" t="s">
         <v>817</v>
-      </c>
-    </row>
-    <row r="3" spans="1:33" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>818</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>38</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>39</v>
@@ -16420,7 +16423,7 @@
         <v>797</v>
       </c>
       <c r="K3" s="8" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="L3" s="8">
         <v>2025</v>
@@ -16429,52 +16432,52 @@
         <v>799</v>
       </c>
       <c r="N3" s="8" t="s">
+        <v>821</v>
+      </c>
+      <c r="O3" s="8" t="s">
         <v>822</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="P3" s="8" t="s">
         <v>823</v>
       </c>
-      <c r="P3" s="8" t="s">
+      <c r="Q3" s="8" t="s">
         <v>824</v>
       </c>
-      <c r="Q3" s="8" t="s">
+      <c r="R3" s="8" t="s">
         <v>825</v>
       </c>
-      <c r="R3" s="8" t="s">
+      <c r="S3" s="8" t="s">
         <v>826</v>
       </c>
-      <c r="S3" s="8" t="s">
+      <c r="T3" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="U3" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V3" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W3" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X3" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="Y3" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="Z3" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="AA3" s="8" t="s">
         <v>827</v>
       </c>
-      <c r="T3" s="8" t="s">
-        <v>826</v>
-      </c>
-      <c r="U3" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V3" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W3" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X3" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="Y3" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="Z3" s="8" t="s">
-        <v>812</v>
-      </c>
-      <c r="AA3" s="8" t="s">
-        <v>828</v>
-      </c>
       <c r="AB3" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="AC3" s="8" t="s">
         <v>814</v>
-      </c>
-      <c r="AC3" s="8" t="s">
-        <v>815</v>
       </c>
       <c r="AD3" s="8">
         <v>2025</v>
@@ -16483,15 +16486,15 @@
         <v>2024</v>
       </c>
       <c r="AF3" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="AG3" s="8" t="s">
         <v>829</v>
       </c>
-      <c r="AG3" s="8" t="s">
+    </row>
+    <row r="4" spans="1:33" ht="52.8" customHeight="1">
+      <c r="A4" s="8" t="s">
         <v>830</v>
-      </c>
-    </row>
-    <row r="4" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>831</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>89</v>
@@ -16509,7 +16512,7 @@
         <v>26</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H4" s="8">
         <v>2024</v>
@@ -16518,10 +16521,10 @@
         <v>31.3</v>
       </c>
       <c r="J4" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>833</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>834</v>
       </c>
       <c r="L4" s="8">
         <v>2025</v>
@@ -16530,52 +16533,52 @@
         <v>799</v>
       </c>
       <c r="N4" s="8" t="s">
+        <v>834</v>
+      </c>
+      <c r="O4" s="8" t="s">
         <v>835</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="P4" s="8" t="s">
         <v>836</v>
       </c>
-      <c r="P4" s="8" t="s">
+      <c r="Q4" s="8" t="s">
         <v>837</v>
       </c>
-      <c r="Q4" s="8" t="s">
+      <c r="R4" s="8" t="s">
         <v>838</v>
       </c>
-      <c r="R4" s="8" t="s">
+      <c r="S4" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="T4" s="8" t="s">
         <v>839</v>
       </c>
-      <c r="S4" s="8" t="s">
-        <v>839</v>
-      </c>
-      <c r="T4" s="8" t="s">
+      <c r="U4" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V4" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W4" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X4" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="Y4" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="Z4" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="AA4" s="8" t="s">
         <v>840</v>
       </c>
-      <c r="U4" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V4" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W4" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X4" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="Y4" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="Z4" s="8" t="s">
-        <v>812</v>
-      </c>
-      <c r="AA4" s="8" t="s">
-        <v>841</v>
-      </c>
       <c r="AB4" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="AC4" s="8" t="s">
         <v>814</v>
-      </c>
-      <c r="AC4" s="8" t="s">
-        <v>815</v>
       </c>
       <c r="AD4" s="8">
         <v>2025</v>
@@ -16584,21 +16587,21 @@
         <v>2024</v>
       </c>
       <c r="AF4" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="AG4" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="AG4" s="8" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="5" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:33" ht="39.6" customHeight="1">
       <c r="A5" s="8" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>95</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>97</v>
@@ -16610,7 +16613,7 @@
         <v>26</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H5" s="8">
         <v>2024</v>
@@ -16619,10 +16622,10 @@
         <v>16</v>
       </c>
       <c r="J5" s="8" t="s">
+        <v>844</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>845</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>846</v>
       </c>
       <c r="L5" s="8">
         <v>2025</v>
@@ -16631,52 +16634,52 @@
         <v>799</v>
       </c>
       <c r="N5" s="8" t="s">
+        <v>846</v>
+      </c>
+      <c r="O5" s="8" t="s">
         <v>847</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="P5" s="8" t="s">
         <v>848</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="Q5" s="8" t="s">
         <v>849</v>
       </c>
-      <c r="Q5" s="8" t="s">
+      <c r="R5" s="8" t="s">
         <v>850</v>
       </c>
-      <c r="R5" s="8" t="s">
+      <c r="S5" s="8" t="s">
         <v>851</v>
       </c>
-      <c r="S5" s="8" t="s">
+      <c r="T5" s="8" t="s">
+        <v>850</v>
+      </c>
+      <c r="U5" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V5" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W5" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X5" s="8" t="s">
         <v>852</v>
       </c>
-      <c r="T5" s="8" t="s">
-        <v>851</v>
-      </c>
-      <c r="U5" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V5" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W5" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X5" s="8" t="s">
+      <c r="Y5" s="8" t="s">
         <v>853</v>
       </c>
-      <c r="Y5" s="8" t="s">
+      <c r="Z5" s="8" t="s">
         <v>854</v>
       </c>
-      <c r="Z5" s="8" t="s">
+      <c r="AA5" s="8" t="s">
         <v>855</v>
       </c>
-      <c r="AA5" s="8" t="s">
+      <c r="AB5" s="8" t="s">
         <v>856</v>
       </c>
-      <c r="AB5" s="8" t="s">
-        <v>857</v>
-      </c>
       <c r="AC5" s="8" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD5" s="8">
         <v>2025</v>
@@ -16685,21 +16688,21 @@
         <v>2024</v>
       </c>
       <c r="AF5" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="AG5" s="8" t="s">
         <v>858</v>
       </c>
-      <c r="AG5" s="8" t="s">
+    </row>
+    <row r="6" spans="1:33" ht="39.6" customHeight="1">
+      <c r="A6" s="8" t="s">
         <v>859</v>
-      </c>
-    </row>
-    <row r="6" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>860</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>101</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>103</v>
@@ -16720,10 +16723,10 @@
         <v>27</v>
       </c>
       <c r="J6" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>862</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>863</v>
       </c>
       <c r="L6" s="8">
         <v>2026</v>
@@ -16732,52 +16735,52 @@
         <v>799</v>
       </c>
       <c r="N6" s="8" t="s">
+        <v>863</v>
+      </c>
+      <c r="O6" s="8" t="s">
         <v>864</v>
       </c>
-      <c r="O6" s="8" t="s">
+      <c r="P6" s="8" t="s">
         <v>865</v>
       </c>
-      <c r="P6" s="8" t="s">
+      <c r="Q6" s="8" t="s">
         <v>866</v>
       </c>
-      <c r="Q6" s="8" t="s">
+      <c r="R6" s="8" t="s">
         <v>867</v>
       </c>
-      <c r="R6" s="8" t="s">
+      <c r="S6" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="T6" s="8" t="s">
         <v>868</v>
       </c>
-      <c r="S6" s="8" t="s">
+      <c r="U6" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V6" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W6" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="T6" s="8" t="s">
+      <c r="X6" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y6" s="8" t="s">
         <v>869</v>
       </c>
-      <c r="U6" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V6" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W6" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X6" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y6" s="8" t="s">
+      <c r="Z6" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="Z6" s="8" t="s">
+      <c r="AA6" s="8" t="s">
         <v>871</v>
       </c>
-      <c r="AA6" s="8" t="s">
-        <v>872</v>
-      </c>
       <c r="AB6" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AC6" s="8" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AD6" s="8">
         <v>2026</v>
@@ -16786,21 +16789,21 @@
         <v>2024</v>
       </c>
       <c r="AF6" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AG6" s="8" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" ht="39.6" customHeight="1">
+      <c r="A7" s="8" t="s">
         <v>873</v>
-      </c>
-    </row>
-    <row r="7" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>874</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>107</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>109</v>
@@ -16821,10 +16824,10 @@
         <v>5</v>
       </c>
       <c r="J7" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>862</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>863</v>
       </c>
       <c r="L7" s="8">
         <v>2026</v>
@@ -16833,52 +16836,52 @@
         <v>799</v>
       </c>
       <c r="N7" s="8" t="s">
+        <v>863</v>
+      </c>
+      <c r="O7" s="8" t="s">
         <v>864</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="P7" s="8" t="s">
         <v>865</v>
       </c>
-      <c r="P7" s="8" t="s">
+      <c r="Q7" s="8" t="s">
         <v>866</v>
       </c>
-      <c r="Q7" s="8" t="s">
-        <v>867</v>
-      </c>
       <c r="R7" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="S7" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="T7" s="8" t="s">
+        <v>868</v>
+      </c>
+      <c r="U7" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V7" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W7" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X7" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y7" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z7" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA7" s="8" t="s">
         <v>876</v>
       </c>
-      <c r="S7" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="T7" s="8" t="s">
-        <v>869</v>
-      </c>
-      <c r="U7" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V7" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W7" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X7" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y7" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z7" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA7" s="8" t="s">
-        <v>877</v>
-      </c>
       <c r="AB7" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AC7" s="8" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AD7" s="8">
         <v>2026</v>
@@ -16887,15 +16890,15 @@
         <v>2024</v>
       </c>
       <c r="AF7" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AG7" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="8" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" ht="39.6" customHeight="1">
       <c r="A8" s="8" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>120</v>
@@ -16922,10 +16925,10 @@
         <v>149</v>
       </c>
       <c r="J8" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="K8" s="8" t="s">
         <v>862</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>863</v>
       </c>
       <c r="L8" s="8">
         <v>2026</v>
@@ -16934,13 +16937,13 @@
         <v>799</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="O8" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="P8" s="8" t="s">
         <v>879</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>880</v>
       </c>
       <c r="Q8" s="8" t="s">
         <v>121</v>
@@ -16949,37 +16952,37 @@
         <v>121</v>
       </c>
       <c r="S8" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="T8" s="8" t="s">
+        <v>880</v>
+      </c>
+      <c r="U8" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V8" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W8" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="T8" s="8" t="s">
+      <c r="X8" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y8" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z8" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA8" s="8" t="s">
         <v>881</v>
       </c>
-      <c r="U8" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V8" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W8" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X8" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y8" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z8" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA8" s="8" t="s">
+      <c r="AB8" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="AC8" s="8" t="s">
         <v>882</v>
-      </c>
-      <c r="AB8" s="8" t="s">
-        <v>814</v>
-      </c>
-      <c r="AC8" s="8" t="s">
-        <v>883</v>
       </c>
       <c r="AD8" s="8">
         <v>2026</v>
@@ -16988,15 +16991,15 @@
         <v>2024</v>
       </c>
       <c r="AF8" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="9" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" ht="39.6" customHeight="1">
       <c r="A9" s="8" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>125</v>
@@ -17023,10 +17026,10 @@
         <v>98</v>
       </c>
       <c r="J9" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="K9" s="8" t="s">
         <v>862</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>863</v>
       </c>
       <c r="L9" s="8">
         <v>2026</v>
@@ -17035,52 +17038,52 @@
         <v>799</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="O9" s="8" t="s">
+        <v>884</v>
+      </c>
+      <c r="P9" s="8" t="s">
         <v>885</v>
       </c>
-      <c r="P9" s="8" t="s">
+      <c r="Q9" s="8" t="s">
         <v>886</v>
       </c>
-      <c r="Q9" s="8" t="s">
+      <c r="R9" s="8" t="s">
         <v>887</v>
       </c>
-      <c r="R9" s="8" t="s">
+      <c r="S9" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="T9" s="8" t="s">
         <v>888</v>
       </c>
-      <c r="S9" s="8" t="s">
+      <c r="U9" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V9" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W9" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="T9" s="8" t="s">
+      <c r="X9" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y9" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z9" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA9" s="8" t="s">
         <v>889</v>
       </c>
-      <c r="U9" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V9" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W9" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X9" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y9" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z9" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA9" s="8" t="s">
+      <c r="AB9" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="AC9" s="8" t="s">
         <v>890</v>
-      </c>
-      <c r="AB9" s="8" t="s">
-        <v>814</v>
-      </c>
-      <c r="AC9" s="8" t="s">
-        <v>891</v>
       </c>
       <c r="AD9" s="8">
         <v>2026</v>
@@ -17089,15 +17092,15 @@
         <v>2024</v>
       </c>
       <c r="AF9" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AG9" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="10" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" ht="39.6" customHeight="1">
       <c r="A10" s="8" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>129</v>
@@ -17124,10 +17127,10 @@
         <v>36</v>
       </c>
       <c r="J10" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="K10" s="8" t="s">
         <v>862</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>863</v>
       </c>
       <c r="L10" s="8">
         <v>2026</v>
@@ -17136,52 +17139,52 @@
         <v>799</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="O10" s="8" t="s">
+        <v>892</v>
+      </c>
+      <c r="P10" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="P10" s="8" t="s">
+      <c r="Q10" s="8" t="s">
+        <v>893</v>
+      </c>
+      <c r="R10" s="8" t="s">
         <v>894</v>
       </c>
-      <c r="Q10" s="8" t="s">
-        <v>894</v>
-      </c>
-      <c r="R10" s="8" t="s">
+      <c r="S10" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="T10" s="8" t="s">
         <v>895</v>
       </c>
-      <c r="S10" s="8" t="s">
+      <c r="U10" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V10" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W10" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="T10" s="8" t="s">
+      <c r="X10" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y10" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z10" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA10" s="8" t="s">
         <v>896</v>
       </c>
-      <c r="U10" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V10" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W10" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X10" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y10" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z10" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA10" s="8" t="s">
-        <v>897</v>
-      </c>
       <c r="AB10" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AC10" s="8" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="AD10" s="8">
         <v>2026</v>
@@ -17190,15 +17193,15 @@
         <v>2024</v>
       </c>
       <c r="AF10" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AG10" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="11" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" ht="39.6" customHeight="1">
       <c r="A11" s="8" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>134</v>
@@ -17225,10 +17228,10 @@
         <v>17</v>
       </c>
       <c r="J11" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="K11" s="8" t="s">
         <v>862</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>863</v>
       </c>
       <c r="L11" s="8">
         <v>2026</v>
@@ -17237,52 +17240,52 @@
         <v>799</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="O11" s="8" t="s">
+        <v>892</v>
+      </c>
+      <c r="P11" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="P11" s="8" t="s">
-        <v>894</v>
-      </c>
       <c r="Q11" s="8" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="R11" s="8" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="S11" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="T11" s="8" t="s">
+        <v>895</v>
+      </c>
+      <c r="U11" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V11" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W11" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="T11" s="8" t="s">
+      <c r="X11" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y11" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z11" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA11" s="8" t="s">
         <v>896</v>
       </c>
-      <c r="U11" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V11" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W11" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X11" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y11" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z11" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA11" s="8" t="s">
-        <v>897</v>
-      </c>
       <c r="AB11" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AC11" s="8" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="AD11" s="8">
         <v>2026</v>
@@ -17291,15 +17294,15 @@
         <v>2024</v>
       </c>
       <c r="AF11" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AG11" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="12" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" ht="39.6" customHeight="1">
       <c r="A12" s="8" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>175</v>
@@ -17326,10 +17329,10 @@
         <v>5.5</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="L12" s="8">
         <v>2024</v>
@@ -17338,52 +17341,52 @@
         <v>799</v>
       </c>
       <c r="N12" s="8" t="s">
+        <v>901</v>
+      </c>
+      <c r="O12" s="8" t="s">
         <v>902</v>
       </c>
-      <c r="O12" s="8" t="s">
+      <c r="P12" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="P12" s="8" t="s">
+      <c r="Q12" s="8" t="s">
         <v>904</v>
       </c>
-      <c r="Q12" s="8" t="s">
+      <c r="R12" s="8" t="s">
         <v>905</v>
       </c>
-      <c r="R12" s="8" t="s">
+      <c r="S12" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="S12" s="8" t="s">
+      <c r="T12" s="8" t="s">
+        <v>905</v>
+      </c>
+      <c r="U12" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V12" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W12" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X12" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y12" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z12" s="8" t="s">
         <v>907</v>
       </c>
-      <c r="T12" s="8" t="s">
-        <v>906</v>
-      </c>
-      <c r="U12" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V12" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W12" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X12" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y12" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z12" s="8" t="s">
+      <c r="AA12" s="8" t="s">
         <v>908</v>
       </c>
-      <c r="AA12" s="8" t="s">
+      <c r="AB12" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="AC12" s="8" t="s">
         <v>909</v>
-      </c>
-      <c r="AB12" s="8" t="s">
-        <v>814</v>
-      </c>
-      <c r="AC12" s="8" t="s">
-        <v>910</v>
       </c>
       <c r="AD12" s="8">
         <v>2024</v>
@@ -17392,27 +17395,27 @@
         <v>2024</v>
       </c>
       <c r="AF12" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AG12" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="13" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" ht="39.6" customHeight="1">
       <c r="A13" s="8" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>180</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>182</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>26</v>
@@ -17427,10 +17430,10 @@
         <v>64</v>
       </c>
       <c r="J13" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="K13" s="8" t="s">
         <v>862</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>863</v>
       </c>
       <c r="L13" s="8">
         <v>2026</v>
@@ -17439,52 +17442,52 @@
         <v>799</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="O13" s="8" t="s">
+        <v>913</v>
+      </c>
+      <c r="P13" s="8" t="s">
         <v>914</v>
       </c>
-      <c r="P13" s="8" t="s">
+      <c r="Q13" s="8" t="s">
         <v>915</v>
       </c>
-      <c r="Q13" s="8" t="s">
+      <c r="R13" s="8" t="s">
         <v>916</v>
       </c>
-      <c r="R13" s="8" t="s">
+      <c r="S13" s="8" t="s">
         <v>917</v>
       </c>
-      <c r="S13" s="8" t="s">
+      <c r="T13" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="U13" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V13" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W13" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X13" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y13" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z13" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA13" s="8" t="s">
         <v>918</v>
       </c>
-      <c r="T13" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="U13" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V13" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W13" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X13" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y13" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z13" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA13" s="8" t="s">
+      <c r="AB13" s="8" t="s">
         <v>919</v>
       </c>
-      <c r="AB13" s="8" t="s">
-        <v>920</v>
-      </c>
       <c r="AC13" s="8" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AD13" s="8">
         <v>2026</v>
@@ -17493,21 +17496,21 @@
         <v>2024</v>
       </c>
       <c r="AF13" s="8" t="s">
+        <v>920</v>
+      </c>
+      <c r="AG13" s="8" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" ht="52.8" customHeight="1">
+      <c r="A14" s="8" t="s">
         <v>921</v>
-      </c>
-      <c r="AG13" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="14" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>922</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>189</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>191</v>
@@ -17528,10 +17531,10 @@
         <v>8</v>
       </c>
       <c r="J14" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="K14" s="8" t="s">
         <v>862</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>863</v>
       </c>
       <c r="L14" s="8">
         <v>2026</v>
@@ -17540,52 +17543,52 @@
         <v>799</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="O14" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="P14" s="8" t="s">
         <v>924</v>
       </c>
-      <c r="P14" s="8" t="s">
+      <c r="Q14" s="8" t="s">
         <v>925</v>
       </c>
-      <c r="Q14" s="8" t="s">
+      <c r="R14" s="8" t="s">
         <v>926</v>
       </c>
-      <c r="R14" s="8" t="s">
+      <c r="S14" s="8" t="s">
         <v>927</v>
       </c>
-      <c r="S14" s="8" t="s">
+      <c r="T14" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="U14" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V14" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W14" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X14" s="8" t="s">
         <v>928</v>
       </c>
-      <c r="T14" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="U14" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V14" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W14" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X14" s="8" t="s">
+      <c r="Y14" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="Z14" s="8" t="s">
+        <v>854</v>
+      </c>
+      <c r="AA14" s="8" t="s">
         <v>929</v>
       </c>
-      <c r="Y14" s="8" t="s">
-        <v>854</v>
-      </c>
-      <c r="Z14" s="8" t="s">
-        <v>855</v>
-      </c>
-      <c r="AA14" s="8" t="s">
-        <v>930</v>
-      </c>
       <c r="AB14" s="8" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AC14" s="8" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="AD14" s="8">
         <v>2026</v>
@@ -17594,27 +17597,27 @@
         <v>2024</v>
       </c>
       <c r="AF14" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AG14" s="8" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" ht="52.8" customHeight="1">
       <c r="A15" s="8" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>208</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>210</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>26</v>
@@ -17629,10 +17632,10 @@
         <v>3.9</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L15" s="8">
         <v>2021</v>
@@ -17641,52 +17644,52 @@
         <v>799</v>
       </c>
       <c r="N15" s="8" t="s">
+        <v>933</v>
+      </c>
+      <c r="O15" s="8" t="s">
         <v>934</v>
       </c>
-      <c r="O15" s="8" t="s">
+      <c r="P15" s="8" t="s">
         <v>935</v>
       </c>
-      <c r="P15" s="8" t="s">
+      <c r="Q15" s="8" t="s">
         <v>936</v>
       </c>
-      <c r="Q15" s="8" t="s">
+      <c r="R15" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="R15" s="8" t="s">
+      <c r="S15" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="T15" s="8" t="s">
         <v>938</v>
       </c>
-      <c r="S15" s="8" t="s">
+      <c r="U15" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V15" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W15" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="T15" s="8" t="s">
+      <c r="X15" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y15" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z15" s="8" t="s">
         <v>939</v>
       </c>
-      <c r="U15" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V15" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W15" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X15" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y15" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z15" s="8" t="s">
+      <c r="AA15" s="8" t="s">
         <v>940</v>
       </c>
-      <c r="AA15" s="8" t="s">
+      <c r="AB15" s="8" t="s">
         <v>941</v>
       </c>
-      <c r="AB15" s="8" t="s">
+      <c r="AC15" s="8" t="s">
         <v>942</v>
-      </c>
-      <c r="AC15" s="8" t="s">
-        <v>943</v>
       </c>
       <c r="AD15" s="8">
         <v>2021</v>
@@ -17695,33 +17698,33 @@
         <v>2020</v>
       </c>
       <c r="AF15" s="8" t="s">
+        <v>943</v>
+      </c>
+      <c r="AG15" s="8" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" ht="52.8" customHeight="1">
+      <c r="A16" s="8" t="s">
         <v>944</v>
-      </c>
-      <c r="AG15" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>945</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>248</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H16" s="8">
         <v>2020</v>
@@ -17730,10 +17733,10 @@
         <v>76</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L16" s="8">
         <v>2021</v>
@@ -17742,52 +17745,52 @@
         <v>799</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="O16" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="P16" s="8" t="s">
         <v>949</v>
       </c>
-      <c r="P16" s="8" t="s">
+      <c r="Q16" s="8" t="s">
         <v>950</v>
       </c>
-      <c r="Q16" s="8" t="s">
+      <c r="R16" s="8" t="s">
         <v>951</v>
       </c>
-      <c r="R16" s="8" t="s">
+      <c r="S16" s="8" t="s">
         <v>952</v>
       </c>
-      <c r="S16" s="8" t="s">
+      <c r="T16" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V16" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W16" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X16" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y16" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z16" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA16" s="8" t="s">
         <v>953</v>
       </c>
-      <c r="T16" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="U16" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V16" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W16" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X16" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y16" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z16" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA16" s="8" t="s">
-        <v>954</v>
-      </c>
       <c r="AB16" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AC16" s="8" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AD16" s="8">
         <v>2021</v>
@@ -17796,27 +17799,27 @@
         <v>2020</v>
       </c>
       <c r="AF16" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AG16" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" ht="39.6" customHeight="1">
       <c r="A17" s="8" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>270</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>272</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>26</v>
@@ -17846,49 +17849,49 @@
         <v>800</v>
       </c>
       <c r="O17" s="8" t="s">
+        <v>956</v>
+      </c>
+      <c r="P17" s="8" t="s">
         <v>957</v>
       </c>
-      <c r="P17" s="8" t="s">
+      <c r="Q17" s="8" t="s">
         <v>958</v>
       </c>
-      <c r="Q17" s="8" t="s">
+      <c r="R17" s="8" t="s">
         <v>959</v>
       </c>
-      <c r="R17" s="8" t="s">
+      <c r="S17" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="T17" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V17" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W17" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X17" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="Y17" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="Z17" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="AA17" s="8" t="s">
         <v>960</v>
       </c>
-      <c r="S17" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="T17" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="U17" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V17" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W17" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X17" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="Y17" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="Z17" s="8" t="s">
-        <v>812</v>
-      </c>
-      <c r="AA17" s="8" t="s">
-        <v>961</v>
-      </c>
       <c r="AB17" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="AC17" s="8" t="s">
         <v>814</v>
-      </c>
-      <c r="AC17" s="8" t="s">
-        <v>815</v>
       </c>
       <c r="AD17" s="8">
         <v>2025</v>
@@ -17897,27 +17900,27 @@
         <v>2024</v>
       </c>
       <c r="AF17" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="AG17" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="AG17" s="8" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:33" ht="39.6" customHeight="1">
       <c r="A18" s="8" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>275</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>277</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>39</v>
@@ -17947,49 +17950,49 @@
         <v>800</v>
       </c>
       <c r="O18" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="P18" s="8" t="s">
         <v>965</v>
       </c>
-      <c r="P18" s="8" t="s">
+      <c r="Q18" s="8" t="s">
         <v>966</v>
       </c>
-      <c r="Q18" s="8" t="s">
+      <c r="R18" s="8" t="s">
         <v>967</v>
       </c>
-      <c r="R18" s="8" t="s">
+      <c r="S18" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="T18" s="8" t="s">
         <v>968</v>
       </c>
-      <c r="S18" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="T18" s="8" t="s">
+      <c r="U18" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V18" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W18" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X18" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="Y18" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="Z18" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="AA18" s="8" t="s">
         <v>969</v>
       </c>
-      <c r="U18" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V18" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W18" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X18" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="Y18" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="Z18" s="8" t="s">
-        <v>812</v>
-      </c>
-      <c r="AA18" s="8" t="s">
-        <v>970</v>
-      </c>
       <c r="AB18" s="8" t="s">
+        <v>813</v>
+      </c>
+      <c r="AC18" s="8" t="s">
         <v>814</v>
-      </c>
-      <c r="AC18" s="8" t="s">
-        <v>815</v>
       </c>
       <c r="AD18" s="8">
         <v>2025</v>
@@ -17998,27 +18001,27 @@
         <v>2024</v>
       </c>
       <c r="AF18" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="AG18" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="AG18" s="8" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:33" ht="52.8" customHeight="1">
       <c r="A19" s="8" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>300</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>302</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>26</v>
@@ -18033,10 +18036,10 @@
         <v>19.7</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L19" s="8">
         <v>2021</v>
@@ -18045,52 +18048,52 @@
         <v>799</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="O19" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="P19" s="8" t="s">
         <v>974</v>
       </c>
-      <c r="P19" s="8" t="s">
+      <c r="Q19" s="8" t="s">
         <v>975</v>
       </c>
-      <c r="Q19" s="8" t="s">
+      <c r="R19" s="8" t="s">
         <v>976</v>
       </c>
-      <c r="R19" s="8" t="s">
+      <c r="S19" s="8" t="s">
         <v>977</v>
       </c>
-      <c r="S19" s="8" t="s">
+      <c r="T19" s="8" t="s">
         <v>978</v>
       </c>
-      <c r="T19" s="8" t="s">
+      <c r="U19" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V19" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W19" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X19" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y19" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z19" s="8" t="s">
         <v>979</v>
       </c>
-      <c r="U19" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V19" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W19" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X19" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y19" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z19" s="8" t="s">
+      <c r="AA19" s="8" t="s">
         <v>980</v>
       </c>
-      <c r="AA19" s="8" t="s">
+      <c r="AB19" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="AC19" s="8" t="s">
         <v>981</v>
-      </c>
-      <c r="AB19" s="8" t="s">
-        <v>920</v>
-      </c>
-      <c r="AC19" s="8" t="s">
-        <v>982</v>
       </c>
       <c r="AD19" s="8">
         <v>2021</v>
@@ -18099,27 +18102,27 @@
         <v>2020</v>
       </c>
       <c r="AF19" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="AG19" s="8" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" ht="52.8" customHeight="1">
+      <c r="A20" s="8" t="s">
         <v>983</v>
-      </c>
-      <c r="AG19" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
-        <v>984</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>305</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>307</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>26</v>
@@ -18134,10 +18137,10 @@
         <v>8.6</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L20" s="8">
         <v>2021</v>
@@ -18146,52 +18149,52 @@
         <v>799</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="O20" s="8" t="s">
+        <v>986</v>
+      </c>
+      <c r="P20" s="8" t="s">
         <v>987</v>
       </c>
-      <c r="P20" s="8" t="s">
+      <c r="Q20" s="8" t="s">
         <v>988</v>
       </c>
-      <c r="Q20" s="8" t="s">
+      <c r="R20" s="8" t="s">
         <v>989</v>
       </c>
-      <c r="R20" s="8" t="s">
+      <c r="S20" s="8" t="s">
         <v>990</v>
       </c>
-      <c r="S20" s="8" t="s">
+      <c r="T20" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="U20" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V20" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W20" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X20" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y20" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z20" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA20" s="8" t="s">
         <v>991</v>
       </c>
-      <c r="T20" s="8" t="s">
-        <v>979</v>
-      </c>
-      <c r="U20" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V20" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W20" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X20" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y20" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z20" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA20" s="8" t="s">
-        <v>992</v>
-      </c>
       <c r="AB20" s="8" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AC20" s="8" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="AD20" s="8">
         <v>2021</v>
@@ -18200,27 +18203,27 @@
         <v>2020</v>
       </c>
       <c r="AF20" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AG20" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="21" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" ht="52.8" customHeight="1">
       <c r="A21" s="8" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>310</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>312</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>26</v>
@@ -18235,10 +18238,10 @@
         <v>0.3</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L21" s="8">
         <v>2021</v>
@@ -18247,52 +18250,52 @@
         <v>799</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="O21" s="8" t="s">
+        <v>994</v>
+      </c>
+      <c r="P21" s="8" t="s">
         <v>995</v>
       </c>
-      <c r="P21" s="8" t="s">
+      <c r="Q21" s="8" t="s">
         <v>996</v>
       </c>
-      <c r="Q21" s="8" t="s">
+      <c r="R21" s="8" t="s">
         <v>997</v>
       </c>
-      <c r="R21" s="8" t="s">
+      <c r="S21" s="8" t="s">
         <v>998</v>
       </c>
-      <c r="S21" s="8" t="s">
+      <c r="T21" s="8" t="s">
         <v>999</v>
       </c>
-      <c r="T21" s="8" t="s">
+      <c r="U21" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V21" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W21" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X21" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="Y21" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="Z21" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="AA21" s="8" t="s">
         <v>1000</v>
       </c>
-      <c r="U21" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V21" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W21" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X21" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="Y21" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="Z21" s="8" t="s">
-        <v>812</v>
-      </c>
-      <c r="AA21" s="8" t="s">
-        <v>1001</v>
-      </c>
       <c r="AB21" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AC21" s="8" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AD21" s="8">
         <v>2021</v>
@@ -18301,21 +18304,21 @@
         <v>2020</v>
       </c>
       <c r="AF21" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="AG21" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="AG21" s="8" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:33" ht="66" customHeight="1">
       <c r="A22" s="8" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>317</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>319</v>
@@ -18336,10 +18339,10 @@
         <v>17.7</v>
       </c>
       <c r="J22" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>1004</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>1005</v>
       </c>
       <c r="L22" s="8">
         <v>2025</v>
@@ -18348,52 +18351,52 @@
         <v>799</v>
       </c>
       <c r="N22" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="O22" s="8" t="s">
         <v>1006</v>
       </c>
-      <c r="O22" s="8" t="s">
+      <c r="P22" s="8" t="s">
         <v>1007</v>
       </c>
-      <c r="P22" s="8" t="s">
+      <c r="Q22" s="8" t="s">
         <v>1008</v>
       </c>
-      <c r="Q22" s="8" t="s">
+      <c r="R22" s="8" t="s">
         <v>1009</v>
       </c>
-      <c r="R22" s="8" t="s">
+      <c r="S22" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="T22" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="U22" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V22" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W22" s="8" t="s">
         <v>1010</v>
       </c>
-      <c r="S22" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="T22" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="U22" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V22" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W22" s="8" t="s">
+      <c r="X22" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y22" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z22" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA22" s="8" t="s">
         <v>1011</v>
       </c>
-      <c r="X22" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y22" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z22" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA22" s="8" t="s">
-        <v>1012</v>
-      </c>
       <c r="AB22" s="8" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AC22" s="8" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD22" s="8">
         <v>2025</v>
@@ -18402,15 +18405,15 @@
         <v>2024</v>
       </c>
       <c r="AF22" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AG22" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" ht="39.6" customHeight="1">
       <c r="A23" s="8" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>330</v>
@@ -18437,10 +18440,10 @@
         <v>39.6</v>
       </c>
       <c r="J23" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K23" s="8" t="s">
         <v>1004</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>1005</v>
       </c>
       <c r="L23" s="8">
         <v>2025</v>
@@ -18449,52 +18452,52 @@
         <v>799</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="O23" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="Q23" s="8" t="s">
         <v>1014</v>
       </c>
-      <c r="P23" s="8" t="s">
-        <v>1008</v>
-      </c>
-      <c r="Q23" s="8" t="s">
+      <c r="R23" s="8" t="s">
         <v>1015</v>
-      </c>
-      <c r="R23" s="8" t="s">
-        <v>1016</v>
       </c>
       <c r="S23" s="8" t="s">
         <v>187</v>
       </c>
       <c r="T23" s="8" t="s">
+        <v>1016</v>
+      </c>
+      <c r="U23" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V23" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W23" s="8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="X23" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y23" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z23" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA23" s="8" t="s">
         <v>1017</v>
       </c>
-      <c r="U23" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V23" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W23" s="8" t="s">
-        <v>1011</v>
-      </c>
-      <c r="X23" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y23" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z23" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA23" s="8" t="s">
+      <c r="AB23" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="AC23" s="8" t="s">
         <v>1018</v>
-      </c>
-      <c r="AB23" s="8" t="s">
-        <v>920</v>
-      </c>
-      <c r="AC23" s="8" t="s">
-        <v>1019</v>
       </c>
       <c r="AD23" s="8">
         <v>2025</v>
@@ -18503,27 +18506,27 @@
         <v>2023</v>
       </c>
       <c r="AF23" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AG23" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" ht="52.8" customHeight="1">
       <c r="A24" s="8" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>335</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>337</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>26</v>
@@ -18538,10 +18541,10 @@
         <v>63.1</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L24" s="8">
         <v>2021</v>
@@ -18550,52 +18553,52 @@
         <v>799</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="P24" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="Q24" s="8" t="s">
         <v>1023</v>
       </c>
-      <c r="Q24" s="8" t="s">
+      <c r="R24" s="8" t="s">
         <v>1024</v>
       </c>
-      <c r="R24" s="8" t="s">
+      <c r="S24" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="T24" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="U24" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V24" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W24" s="8" t="s">
         <v>1025</v>
       </c>
-      <c r="S24" s="8" t="s">
-        <v>991</v>
-      </c>
-      <c r="T24" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="U24" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V24" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W24" s="8" t="s">
+      <c r="X24" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y24" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z24" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA24" s="8" t="s">
         <v>1026</v>
       </c>
-      <c r="X24" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y24" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z24" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA24" s="8" t="s">
-        <v>1027</v>
-      </c>
       <c r="AB24" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AC24" s="8" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AD24" s="8">
         <v>2021</v>
@@ -18604,15 +18607,15 @@
         <v>2020</v>
       </c>
       <c r="AF24" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AG24" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" ht="39.6" customHeight="1">
       <c r="A25" s="8" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>399</v>
@@ -18654,49 +18657,49 @@
         <v>800</v>
       </c>
       <c r="O25" s="8" t="s">
+        <v>1028</v>
+      </c>
+      <c r="P25" s="8" t="s">
         <v>1029</v>
       </c>
-      <c r="P25" s="8" t="s">
+      <c r="Q25" s="8" t="s">
         <v>1030</v>
       </c>
-      <c r="Q25" s="8" t="s">
+      <c r="R25" s="8" t="s">
         <v>1031</v>
       </c>
-      <c r="R25" s="8" t="s">
+      <c r="S25" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="T25" s="8" t="s">
         <v>1032</v>
       </c>
-      <c r="S25" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="T25" s="8" t="s">
+      <c r="U25" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V25" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W25" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X25" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y25" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z25" s="8" t="s">
         <v>1033</v>
       </c>
-      <c r="U25" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V25" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W25" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X25" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y25" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z25" s="8" t="s">
+      <c r="AA25" s="8" t="s">
         <v>1034</v>
       </c>
-      <c r="AA25" s="8" t="s">
-        <v>1035</v>
-      </c>
       <c r="AB25" s="8" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AC25" s="8" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="AD25" s="8">
         <v>2025</v>
@@ -18705,15 +18708,15 @@
         <v>2024</v>
       </c>
       <c r="AF25" s="8" t="s">
+        <v>1035</v>
+      </c>
+      <c r="AG25" s="8" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" ht="52.8" customHeight="1">
+      <c r="A26" s="8" t="s">
         <v>1036</v>
-      </c>
-      <c r="AG25" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
-        <v>1037</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>414</v>
@@ -18740,10 +18743,10 @@
         <v>6.5</v>
       </c>
       <c r="J26" s="8" t="s">
+        <v>1037</v>
+      </c>
+      <c r="K26" s="8" t="s">
         <v>1038</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>1039</v>
       </c>
       <c r="L26" s="8">
         <v>2025</v>
@@ -18752,52 +18755,52 @@
         <v>799</v>
       </c>
       <c r="N26" s="8" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O26" s="8" t="s">
         <v>1040</v>
       </c>
-      <c r="O26" s="8" t="s">
+      <c r="P26" s="8" t="s">
         <v>1041</v>
-      </c>
-      <c r="P26" s="8" t="s">
-        <v>1042</v>
       </c>
       <c r="Q26" s="8" t="s">
         <v>415</v>
       </c>
       <c r="R26" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="S26" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="T26" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="U26" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V26" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W26" s="8" t="s">
         <v>1043</v>
       </c>
-      <c r="S26" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="T26" s="8" t="s">
-        <v>840</v>
-      </c>
-      <c r="U26" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V26" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W26" s="8" t="s">
+      <c r="X26" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y26" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z26" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA26" s="8" t="s">
         <v>1044</v>
       </c>
-      <c r="X26" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y26" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z26" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA26" s="8" t="s">
-        <v>1045</v>
-      </c>
       <c r="AB26" s="8" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AC26" s="8" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD26" s="8">
         <v>2025</v>
@@ -18806,21 +18809,21 @@
         <v>2024</v>
       </c>
       <c r="AF26" s="8" t="s">
+        <v>1045</v>
+      </c>
+      <c r="AG26" s="8" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" ht="39.6" customHeight="1">
+      <c r="A27" s="8" t="s">
         <v>1046</v>
-      </c>
-      <c r="AG26" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="27" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
-        <v>1047</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>424</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>426</v>
@@ -18841,10 +18844,10 @@
         <v>85.5</v>
       </c>
       <c r="J27" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K27" s="8" t="s">
         <v>1004</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>1005</v>
       </c>
       <c r="L27" s="8">
         <v>2025</v>
@@ -18853,52 +18856,52 @@
         <v>799</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="O27" s="8" t="s">
+        <v>1048</v>
+      </c>
+      <c r="P27" s="8" t="s">
         <v>1049</v>
       </c>
-      <c r="P27" s="8" t="s">
+      <c r="Q27" s="8" t="s">
         <v>1050</v>
       </c>
-      <c r="Q27" s="8" t="s">
+      <c r="R27" s="8" t="s">
         <v>1051</v>
       </c>
-      <c r="R27" s="8" t="s">
+      <c r="S27" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="T27" s="8" t="s">
         <v>1052</v>
       </c>
-      <c r="S27" s="8" t="s">
-        <v>840</v>
-      </c>
-      <c r="T27" s="8" t="s">
+      <c r="U27" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V27" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W27" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X27" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="Y27" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="Z27" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="AA27" s="8" t="s">
         <v>1053</v>
       </c>
-      <c r="U27" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V27" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W27" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X27" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="Y27" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="Z27" s="8" t="s">
-        <v>812</v>
-      </c>
-      <c r="AA27" s="8" t="s">
-        <v>1054</v>
-      </c>
       <c r="AB27" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AC27" s="8" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD27" s="8">
         <v>2025</v>
@@ -18907,21 +18910,21 @@
         <v>2024</v>
       </c>
       <c r="AF27" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="AG27" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="AG27" s="8" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="28" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:33" ht="52.8" customHeight="1">
       <c r="A28" s="8" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>429</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>431</v>
@@ -18942,25 +18945,25 @@
         <v>3496.2608515765401</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="L28" s="8">
         <v>2024</v>
       </c>
       <c r="M28" s="8" t="s">
+        <v>1057</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="O28" s="8" t="s">
         <v>1058</v>
       </c>
-      <c r="N28" s="8" t="s">
-        <v>1006</v>
-      </c>
-      <c r="O28" s="8" t="s">
+      <c r="P28" s="8" t="s">
         <v>1059</v>
-      </c>
-      <c r="P28" s="8" t="s">
-        <v>1060</v>
       </c>
       <c r="Q28" s="8" t="s">
         <v>434</v>
@@ -18969,37 +18972,37 @@
         <v>434</v>
       </c>
       <c r="S28" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="T28" s="8" t="s">
+        <v>1060</v>
+      </c>
+      <c r="U28" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V28" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W28" s="8" t="s">
+        <v>1043</v>
+      </c>
+      <c r="X28" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y28" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z28" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA28" s="8" t="s">
         <v>1061</v>
       </c>
-      <c r="U28" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V28" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W28" s="8" t="s">
-        <v>1044</v>
-      </c>
-      <c r="X28" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y28" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z28" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA28" s="8" t="s">
-        <v>1062</v>
-      </c>
       <c r="AB28" s="8" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AC28" s="8" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="AD28" s="8">
         <v>2024</v>
@@ -19008,15 +19011,15 @@
         <v>2023</v>
       </c>
       <c r="AF28" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AG28" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="29" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" ht="39.6" customHeight="1">
       <c r="A29" s="8" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>436</v>
@@ -19043,10 +19046,10 @@
         <v>14.93</v>
       </c>
       <c r="J29" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K29" s="8" t="s">
         <v>1004</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>1005</v>
       </c>
       <c r="L29" s="8">
         <v>2025</v>
@@ -19055,52 +19058,52 @@
         <v>799</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="O29" s="8" t="s">
+        <v>1063</v>
+      </c>
+      <c r="P29" s="8" t="s">
         <v>1064</v>
       </c>
-      <c r="P29" s="8" t="s">
+      <c r="Q29" s="8" t="s">
         <v>1065</v>
-      </c>
-      <c r="Q29" s="8" t="s">
-        <v>1066</v>
       </c>
       <c r="R29" s="8" t="s">
         <v>439</v>
       </c>
       <c r="S29" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="T29" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="U29" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V29" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W29" s="8" t="s">
         <v>808</v>
       </c>
-      <c r="U29" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V29" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W29" s="8" t="s">
+      <c r="X29" s="8" t="s">
         <v>809</v>
       </c>
-      <c r="X29" s="8" t="s">
+      <c r="Y29" s="8" t="s">
         <v>810</v>
       </c>
-      <c r="Y29" s="8" t="s">
+      <c r="Z29" s="8" t="s">
         <v>811</v>
       </c>
-      <c r="Z29" s="8" t="s">
-        <v>812</v>
-      </c>
       <c r="AA29" s="8" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="AB29" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AC29" s="8" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD29" s="8">
         <v>2025</v>
@@ -19109,21 +19112,21 @@
         <v>2024</v>
       </c>
       <c r="AF29" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="AG29" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="AG29" s="8" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="30" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:33" ht="39.6" customHeight="1">
       <c r="A30" s="8" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>441</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>443</v>
@@ -19144,10 +19147,10 @@
         <v>26.8</v>
       </c>
       <c r="J30" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K30" s="8" t="s">
         <v>1004</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>1005</v>
       </c>
       <c r="L30" s="8">
         <v>2025</v>
@@ -19156,52 +19159,52 @@
         <v>799</v>
       </c>
       <c r="N30" s="8" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="O30" s="8" t="s">
+        <v>1069</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>1070</v>
       </c>
-      <c r="P30" s="8" t="s">
+      <c r="Q30" s="8" t="s">
         <v>1071</v>
       </c>
-      <c r="Q30" s="8" t="s">
+      <c r="R30" s="8" t="s">
         <v>1072</v>
       </c>
-      <c r="R30" s="8" t="s">
+      <c r="S30" s="8" t="s">
         <v>1073</v>
       </c>
-      <c r="S30" s="8" t="s">
+      <c r="T30" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="U30" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V30" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W30" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X30" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y30" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z30" s="8" t="s">
         <v>1074</v>
       </c>
-      <c r="T30" s="8" t="s">
-        <v>840</v>
-      </c>
-      <c r="U30" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V30" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W30" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X30" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y30" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z30" s="8" t="s">
+      <c r="AA30" s="8" t="s">
         <v>1075</v>
       </c>
-      <c r="AA30" s="8" t="s">
-        <v>1076</v>
-      </c>
       <c r="AB30" s="8" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AC30" s="8" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD30" s="8">
         <v>2025</v>
@@ -19210,21 +19213,21 @@
         <v>2024</v>
       </c>
       <c r="AF30" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AG30" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="31" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" ht="39.6" customHeight="1">
       <c r="A31" s="8" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>448</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>450</v>
@@ -19260,49 +19263,49 @@
         <v>800</v>
       </c>
       <c r="O31" s="8" t="s">
+        <v>1078</v>
+      </c>
+      <c r="P31" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="Q31" s="8" t="s">
         <v>1079</v>
       </c>
-      <c r="P31" s="8" t="s">
-        <v>1008</v>
-      </c>
-      <c r="Q31" s="8" t="s">
+      <c r="R31" s="8" t="s">
         <v>1080</v>
       </c>
-      <c r="R31" s="8" t="s">
+      <c r="S31" s="8" t="s">
         <v>1081</v>
       </c>
-      <c r="S31" s="8" t="s">
+      <c r="T31" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="U31" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V31" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W31" s="8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="X31" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y31" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z31" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA31" s="8" t="s">
         <v>1082</v>
       </c>
-      <c r="T31" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="U31" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V31" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W31" s="8" t="s">
-        <v>1011</v>
-      </c>
-      <c r="X31" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y31" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z31" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA31" s="8" t="s">
-        <v>1083</v>
-      </c>
       <c r="AB31" s="8" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AC31" s="8" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="AD31" s="8">
         <v>2025</v>
@@ -19311,21 +19314,21 @@
         <v>2024</v>
       </c>
       <c r="AF31" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AG31" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="32" spans="1:33" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" ht="66" customHeight="1">
       <c r="A32" s="8" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>480</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>482</v>
@@ -19337,7 +19340,7 @@
         <v>26</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="H32" s="8">
         <v>2020</v>
@@ -19349,7 +19352,7 @@
         <v>797</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="L32" s="8">
         <v>2024</v>
@@ -19360,40 +19363,40 @@
       <c r="P32" s="8"/>
       <c r="Q32" s="8"/>
       <c r="R32" s="8" t="s">
+        <v>1087</v>
+      </c>
+      <c r="S32" s="8" t="s">
         <v>1088</v>
       </c>
-      <c r="S32" s="8" t="s">
+      <c r="T32" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="U32" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V32" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W32" s="8" t="s">
+        <v>1025</v>
+      </c>
+      <c r="X32" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="Y32" s="8" t="s">
         <v>1089</v>
       </c>
-      <c r="T32" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="U32" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V32" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W32" s="8" t="s">
-        <v>1026</v>
-      </c>
-      <c r="X32" s="8" t="s">
-        <v>929</v>
-      </c>
-      <c r="Y32" s="8" t="s">
+      <c r="Z32" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="Z32" s="8" t="s">
+      <c r="AA32" s="8" t="s">
         <v>1091</v>
       </c>
-      <c r="AA32" s="8" t="s">
+      <c r="AB32" s="8" t="s">
         <v>1092</v>
       </c>
-      <c r="AB32" s="8" t="s">
+      <c r="AC32" s="8" t="s">
         <v>1093</v>
-      </c>
-      <c r="AC32" s="8" t="s">
-        <v>1094</v>
       </c>
       <c r="AD32" s="8">
         <v>2024</v>
@@ -19402,21 +19405,21 @@
         <v>2020</v>
       </c>
       <c r="AF32" s="8" t="s">
+        <v>1094</v>
+      </c>
+      <c r="AG32" s="8" t="s">
         <v>1095</v>
       </c>
-      <c r="AG32" s="8" t="s">
+    </row>
+    <row r="33" spans="1:33" ht="52.8" customHeight="1">
+      <c r="A33" s="8" t="s">
         <v>1096</v>
-      </c>
-    </row>
-    <row r="33" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
-        <v>1097</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>499</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>501</v>
@@ -19437,10 +19440,10 @@
         <v>10</v>
       </c>
       <c r="J33" s="8" t="s">
+        <v>1037</v>
+      </c>
+      <c r="K33" s="8" t="s">
         <v>1038</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>1039</v>
       </c>
       <c r="L33" s="8">
         <v>2025</v>
@@ -19449,52 +19452,52 @@
         <v>799</v>
       </c>
       <c r="N33" s="8" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="O33" s="8" t="s">
+        <v>1098</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q33" s="8" t="s">
         <v>1099</v>
       </c>
-      <c r="P33" s="8" t="s">
-        <v>942</v>
-      </c>
-      <c r="Q33" s="8" t="s">
+      <c r="R33" s="8" t="s">
         <v>1100</v>
       </c>
-      <c r="R33" s="8" t="s">
+      <c r="S33" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="T33" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="U33" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V33" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W33" s="8" t="s">
+        <v>1043</v>
+      </c>
+      <c r="X33" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y33" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z33" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA33" s="8" t="s">
         <v>1101</v>
       </c>
-      <c r="S33" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="T33" s="8" t="s">
-        <v>840</v>
-      </c>
-      <c r="U33" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V33" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W33" s="8" t="s">
-        <v>1044</v>
-      </c>
-      <c r="X33" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y33" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z33" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA33" s="8" t="s">
+      <c r="AB33" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="AC33" s="8" t="s">
         <v>1102</v>
-      </c>
-      <c r="AB33" s="8" t="s">
-        <v>942</v>
-      </c>
-      <c r="AC33" s="8" t="s">
-        <v>1103</v>
       </c>
       <c r="AD33" s="8">
         <v>2025</v>
@@ -19503,15 +19506,15 @@
         <v>2023</v>
       </c>
       <c r="AF33" s="8" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AG33" s="8" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" ht="39.6" customHeight="1">
+      <c r="A34" s="8" t="s">
         <v>1104</v>
-      </c>
-      <c r="AG33" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="34" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>1105</v>
       </c>
       <c r="B34" s="8" t="s">
         <v>504</v>
@@ -19538,10 +19541,10 @@
         <v>5.7</v>
       </c>
       <c r="J34" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K34" s="8" t="s">
         <v>1004</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>1005</v>
       </c>
       <c r="L34" s="8">
         <v>2025</v>
@@ -19550,52 +19553,52 @@
         <v>799</v>
       </c>
       <c r="N34" s="8" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="O34" s="8" t="s">
+        <v>1105</v>
+      </c>
+      <c r="P34" s="8" t="s">
+        <v>1049</v>
+      </c>
+      <c r="Q34" s="8" t="s">
+        <v>1050</v>
+      </c>
+      <c r="R34" s="8" t="s">
         <v>1106</v>
       </c>
-      <c r="P34" s="8" t="s">
-        <v>1050</v>
-      </c>
-      <c r="Q34" s="8" t="s">
-        <v>1051</v>
-      </c>
-      <c r="R34" s="8" t="s">
+      <c r="S34" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="T34" s="8" t="s">
+        <v>1052</v>
+      </c>
+      <c r="U34" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V34" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W34" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X34" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="Y34" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="Z34" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="AA34" s="8" t="s">
         <v>1107</v>
       </c>
-      <c r="S34" s="8" t="s">
-        <v>840</v>
-      </c>
-      <c r="T34" s="8" t="s">
-        <v>1053</v>
-      </c>
-      <c r="U34" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V34" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W34" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X34" s="8" t="s">
-        <v>810</v>
-      </c>
-      <c r="Y34" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="Z34" s="8" t="s">
-        <v>812</v>
-      </c>
-      <c r="AA34" s="8" t="s">
-        <v>1108</v>
-      </c>
       <c r="AB34" s="8" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="AC34" s="8" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD34" s="8">
         <v>2025</v>
@@ -19604,21 +19607,21 @@
         <v>2024</v>
       </c>
       <c r="AF34" s="8" t="s">
+        <v>815</v>
+      </c>
+      <c r="AG34" s="8" t="s">
         <v>816</v>
       </c>
-      <c r="AG34" s="8" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="35" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:33" ht="52.8" customHeight="1">
       <c r="A35" s="8" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>531</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>533</v>
@@ -19639,64 +19642,64 @@
         <v>0.2</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="L35" s="8">
         <v>2024</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="N35" s="8" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="O35" s="8" t="s">
+        <v>1111</v>
+      </c>
+      <c r="P35" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="Q35" s="8" t="s">
+        <v>1111</v>
+      </c>
+      <c r="R35" s="8" t="s">
         <v>1112</v>
       </c>
-      <c r="P35" s="8" t="s">
-        <v>1008</v>
-      </c>
-      <c r="Q35" s="8" t="s">
-        <v>1112</v>
-      </c>
-      <c r="R35" s="8" t="s">
+      <c r="S35" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="T35" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="U35" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V35" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W35" s="8" t="s">
+        <v>1043</v>
+      </c>
+      <c r="X35" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="Y35" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="Z35" s="8" t="s">
+        <v>854</v>
+      </c>
+      <c r="AA35" s="8" t="s">
         <v>1113</v>
       </c>
-      <c r="S35" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="T35" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="U35" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V35" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W35" s="8" t="s">
-        <v>1044</v>
-      </c>
-      <c r="X35" s="8" t="s">
-        <v>929</v>
-      </c>
-      <c r="Y35" s="8" t="s">
-        <v>854</v>
-      </c>
-      <c r="Z35" s="8" t="s">
-        <v>855</v>
-      </c>
-      <c r="AA35" s="8" t="s">
-        <v>1114</v>
-      </c>
       <c r="AB35" s="8" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AC35" s="8" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="AD35" s="8">
         <v>2024</v>
@@ -19705,21 +19708,21 @@
         <v>2023</v>
       </c>
       <c r="AF35" s="8" t="s">
+        <v>1114</v>
+      </c>
+      <c r="AG35" s="8" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" ht="52.8" customHeight="1">
+      <c r="A36" s="8" t="s">
         <v>1115</v>
-      </c>
-      <c r="AG35" s="8" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="36" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
-        <v>1116</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>551</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>553</v>
@@ -19755,49 +19758,49 @@
         <v>800</v>
       </c>
       <c r="O36" s="8" t="s">
+        <v>1117</v>
+      </c>
+      <c r="P36" s="8" t="s">
         <v>1118</v>
       </c>
-      <c r="P36" s="8" t="s">
+      <c r="Q36" s="8" t="s">
         <v>1119</v>
       </c>
-      <c r="Q36" s="8" t="s">
+      <c r="R36" s="8" t="s">
         <v>1120</v>
       </c>
-      <c r="R36" s="8" t="s">
+      <c r="S36" s="8" t="s">
         <v>1121</v>
       </c>
-      <c r="S36" s="8" t="s">
+      <c r="T36" s="8" t="s">
         <v>1122</v>
       </c>
-      <c r="T36" s="8" t="s">
+      <c r="U36" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V36" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W36" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X36" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="Y36" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="Z36" s="8" t="s">
+        <v>854</v>
+      </c>
+      <c r="AA36" s="8" t="s">
         <v>1123</v>
       </c>
-      <c r="U36" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V36" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W36" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X36" s="8" t="s">
-        <v>929</v>
-      </c>
-      <c r="Y36" s="8" t="s">
-        <v>854</v>
-      </c>
-      <c r="Z36" s="8" t="s">
-        <v>855</v>
-      </c>
-      <c r="AA36" s="8" t="s">
-        <v>1124</v>
-      </c>
       <c r="AB36" s="8" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AC36" s="8" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="AD36" s="8">
         <v>2025</v>
@@ -19806,27 +19809,27 @@
         <v>2024</v>
       </c>
       <c r="AF36" s="8" t="s">
+        <v>1124</v>
+      </c>
+      <c r="AG36" s="8" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" ht="52.8" customHeight="1">
+      <c r="A37" s="8" t="s">
         <v>1125</v>
-      </c>
-      <c r="AG36" s="8" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="37" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
-        <v>1126</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>605</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>607</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>26</v>
@@ -19841,10 +19844,10 @@
         <v>9</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="L37" s="8">
         <v>2021</v>
@@ -19853,52 +19856,52 @@
         <v>799</v>
       </c>
       <c r="N37" s="8" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="O37" s="8" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="P37" s="8" t="s">
+        <v>1128</v>
+      </c>
+      <c r="Q37" s="8" t="s">
         <v>1129</v>
       </c>
-      <c r="Q37" s="8" t="s">
+      <c r="R37" s="8" t="s">
         <v>1130</v>
       </c>
-      <c r="R37" s="8" t="s">
+      <c r="S37" s="8" t="s">
         <v>1131</v>
       </c>
-      <c r="S37" s="8" t="s">
+      <c r="T37" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="U37" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V37" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W37" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X37" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y37" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z37" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA37" s="8" t="s">
         <v>1132</v>
       </c>
-      <c r="T37" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="U37" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V37" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W37" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X37" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y37" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z37" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA37" s="8" t="s">
-        <v>1133</v>
-      </c>
       <c r="AB37" s="8" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="AC37" s="8" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="AD37" s="8">
         <v>2021</v>
@@ -19907,21 +19910,21 @@
         <v>2020</v>
       </c>
       <c r="AF37" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AG37" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="38" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" ht="39.6" customHeight="1">
       <c r="A38" s="8" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>666</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>667</v>
@@ -19942,64 +19945,64 @@
         <v>0.2</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="K38" s="8" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="L38" s="8">
         <v>2024</v>
       </c>
       <c r="M38" s="8" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="N38" s="8" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="O38" s="8" t="s">
+        <v>1111</v>
+      </c>
+      <c r="P38" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="Q38" s="8" t="s">
+        <v>1111</v>
+      </c>
+      <c r="R38" s="8" t="s">
         <v>1112</v>
       </c>
-      <c r="P38" s="8" t="s">
-        <v>1008</v>
-      </c>
-      <c r="Q38" s="8" t="s">
-        <v>1112</v>
-      </c>
-      <c r="R38" s="8" t="s">
-        <v>1113</v>
-      </c>
       <c r="S38" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="T38" s="8" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="U38" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V38" s="8" t="s">
         <v>807</v>
       </c>
-      <c r="V38" s="8" t="s">
-        <v>808</v>
-      </c>
       <c r="W38" s="8" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="X38" s="8" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="Y38" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="Z38" s="8" t="s">
         <v>854</v>
       </c>
-      <c r="Z38" s="8" t="s">
-        <v>855</v>
-      </c>
       <c r="AA38" s="8" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="AB38" s="8" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AC38" s="8" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="AD38" s="8">
         <v>2024</v>
@@ -20008,27 +20011,27 @@
         <v>2023</v>
       </c>
       <c r="AF38" s="8" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="AG38" s="8" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="39" spans="1:33" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" ht="39.6" customHeight="1">
       <c r="A39" s="8" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>696</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>698</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>26</v>
@@ -20043,10 +20046,10 @@
         <v>16.2</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K39" s="8" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="L39" s="8">
         <v>2023</v>
@@ -20055,52 +20058,52 @@
         <v>799</v>
       </c>
       <c r="N39" s="8" t="s">
+        <v>1138</v>
+      </c>
+      <c r="O39" s="8" t="s">
         <v>1139</v>
       </c>
-      <c r="O39" s="8" t="s">
+      <c r="P39" s="8" t="s">
         <v>1140</v>
       </c>
-      <c r="P39" s="8" t="s">
+      <c r="Q39" s="8" t="s">
         <v>1141</v>
       </c>
-      <c r="Q39" s="8" t="s">
+      <c r="R39" s="8" t="s">
         <v>1142</v>
       </c>
-      <c r="R39" s="8" t="s">
+      <c r="S39" s="8" t="s">
         <v>1143</v>
       </c>
-      <c r="S39" s="8" t="s">
+      <c r="T39" s="8" t="s">
         <v>1144</v>
       </c>
-      <c r="T39" s="8" t="s">
+      <c r="U39" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V39" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W39" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="X39" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y39" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z39" s="8" t="s">
         <v>1145</v>
       </c>
-      <c r="U39" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V39" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W39" s="8" t="s">
-        <v>809</v>
-      </c>
-      <c r="X39" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y39" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z39" s="8" t="s">
+      <c r="AA39" s="8" t="s">
         <v>1146</v>
       </c>
-      <c r="AA39" s="8" t="s">
+      <c r="AB39" s="8" t="s">
+        <v>919</v>
+      </c>
+      <c r="AC39" s="8" t="s">
         <v>1147</v>
-      </c>
-      <c r="AB39" s="8" t="s">
-        <v>920</v>
-      </c>
-      <c r="AC39" s="8" t="s">
-        <v>1148</v>
       </c>
       <c r="AD39" s="8">
         <v>2023</v>
@@ -20109,15 +20112,15 @@
         <v>2022</v>
       </c>
       <c r="AF39" s="8" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="AG39" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="40" spans="1:33" ht="52.8" customHeight="1" x14ac:dyDescent="0.3">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" ht="52.8" customHeight="1">
       <c r="A40" s="8" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>705</v>
@@ -20144,10 +20147,10 @@
         <v>6.5</v>
       </c>
       <c r="J40" s="8" t="s">
+        <v>1037</v>
+      </c>
+      <c r="K40" s="8" t="s">
         <v>1038</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>1039</v>
       </c>
       <c r="L40" s="8">
         <v>2025</v>
@@ -20156,52 +20159,52 @@
         <v>799</v>
       </c>
       <c r="N40" s="8" t="s">
+        <v>1039</v>
+      </c>
+      <c r="O40" s="8" t="s">
         <v>1040</v>
       </c>
-      <c r="O40" s="8" t="s">
+      <c r="P40" s="8" t="s">
         <v>1041</v>
-      </c>
-      <c r="P40" s="8" t="s">
-        <v>1042</v>
       </c>
       <c r="Q40" s="8" t="s">
         <v>415</v>
       </c>
       <c r="R40" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="S40" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="T40" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="U40" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V40" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W40" s="8" t="s">
         <v>1043</v>
       </c>
-      <c r="S40" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="T40" s="8" t="s">
-        <v>840</v>
-      </c>
-      <c r="U40" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V40" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W40" s="8" t="s">
-        <v>1044</v>
-      </c>
       <c r="X40" s="8" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="Y40" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z40" s="8" t="s">
         <v>870</v>
       </c>
-      <c r="Z40" s="8" t="s">
-        <v>871</v>
-      </c>
       <c r="AA40" s="8" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="AB40" s="8" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AC40" s="8" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="AD40" s="8">
         <v>2025</v>
@@ -20210,15 +20213,15 @@
         <v>2024</v>
       </c>
       <c r="AF40" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="AG40" s="8" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" ht="92.4" customHeight="1">
+      <c r="A41" s="8" t="s">
         <v>1151</v>
-      </c>
-      <c r="AG40" s="8" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="41" spans="1:33" ht="92.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="8" t="s">
-        <v>1152</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>709</v>
@@ -20230,13 +20233,13 @@
         <v>711</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="H41" s="8">
         <v>2023</v>
@@ -20245,64 +20248,64 @@
         <v>36</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="L41" s="8">
         <v>2024</v>
       </c>
       <c r="M41" s="8" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="N41" s="8" t="s">
+        <v>1155</v>
+      </c>
+      <c r="O41" s="8" t="s">
         <v>1156</v>
       </c>
-      <c r="O41" s="8" t="s">
+      <c r="P41" s="8" t="s">
         <v>1157</v>
       </c>
-      <c r="P41" s="8" t="s">
+      <c r="Q41" s="8" t="s">
         <v>1158</v>
       </c>
-      <c r="Q41" s="8" t="s">
+      <c r="R41" s="8" t="s">
         <v>1159</v>
       </c>
-      <c r="R41" s="8" t="s">
+      <c r="S41" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="T41" s="8" t="s">
         <v>1160</v>
       </c>
-      <c r="S41" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="T41" s="8" t="s">
+      <c r="U41" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="V41" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="W41" s="8" t="s">
+        <v>1043</v>
+      </c>
+      <c r="X41" s="8" t="s">
+        <v>852</v>
+      </c>
+      <c r="Y41" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="Z41" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="AA41" s="8" t="s">
         <v>1161</v>
       </c>
-      <c r="U41" s="8" t="s">
-        <v>807</v>
-      </c>
-      <c r="V41" s="8" t="s">
-        <v>808</v>
-      </c>
-      <c r="W41" s="8" t="s">
-        <v>1044</v>
-      </c>
-      <c r="X41" s="8" t="s">
-        <v>853</v>
-      </c>
-      <c r="Y41" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="Z41" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="AA41" s="8" t="s">
+      <c r="AB41" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="AC41" s="8" t="s">
         <v>1162</v>
-      </c>
-      <c r="AB41" s="8" t="s">
-        <v>942</v>
-      </c>
-      <c r="AC41" s="8" t="s">
-        <v>1163</v>
       </c>
       <c r="AD41" s="8">
         <v>2024</v>
@@ -20311,10 +20314,10 @@
         <v>2023</v>
       </c>
       <c r="AF41" s="8" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="AG41" s="8" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
   </sheetData>
@@ -20351,7 +20354,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
@@ -20363,9 +20366,9 @@
     <col min="10" max="11" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="14.4" customHeight="1">
       <c r="A1" s="7" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>772</v>
@@ -20383,30 +20386,30 @@
         <v>776</v>
       </c>
       <c r="G1" s="7" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>1166</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>1167</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>787</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="K1" s="7" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="66" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>861</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>862</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>863</v>
       </c>
       <c r="D2" s="8">
         <v>2026</v>
@@ -20415,27 +20418,27 @@
         <v>799</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G2" s="8" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>1170</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>1171</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>1172</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="8" t="s">
         <v>1173</v>
       </c>
-      <c r="K2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:11" ht="66" customHeight="1">
+      <c r="A3" s="8" t="s">
         <v>1174</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>1175</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>797</v>
@@ -20453,30 +20456,30 @@
         <v>800</v>
       </c>
       <c r="G3" s="8" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>1176</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>1177</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="J3" s="8" t="s">
+      <c r="K3" s="8" t="s">
         <v>1178</v>
       </c>
-      <c r="K3" s="8" t="s">
+    </row>
+    <row r="4" spans="1:11" ht="66" customHeight="1">
+      <c r="A4" s="8" t="s">
         <v>1179</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>1180</v>
-      </c>
       <c r="B4" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>833</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>834</v>
       </c>
       <c r="D4" s="8">
         <v>2025</v>
@@ -20485,33 +20488,33 @@
         <v>799</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G4" s="8" t="s">
+        <v>1180</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>1181</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="I4" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="J4" s="8" t="s">
         <v>1182</v>
       </c>
-      <c r="I4" s="8" t="s">
-        <v>811</v>
-      </c>
-      <c r="J4" s="8" t="s">
+      <c r="K4" s="8" t="s">
         <v>1183</v>
       </c>
-      <c r="K4" s="8" t="s">
+    </row>
+    <row r="5" spans="1:11" ht="66" customHeight="1">
+      <c r="A5" s="8" t="s">
         <v>1184</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>1185</v>
-      </c>
       <c r="B5" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>1004</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>1005</v>
       </c>
       <c r="D5" s="8">
         <v>2025</v>
@@ -20520,33 +20523,33 @@
         <v>799</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G5" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J5" s="8" t="s">
         <v>1186</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>1182</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>1172</v>
-      </c>
-      <c r="J5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>1187</v>
       </c>
-      <c r="K5" s="8" t="s">
+    </row>
+    <row r="6" spans="1:11" ht="66" customHeight="1">
+      <c r="A6" s="8" t="s">
         <v>1188</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>1189</v>
-      </c>
       <c r="B6" s="8" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>1038</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>1039</v>
       </c>
       <c r="D6" s="8">
         <v>2025</v>
@@ -20555,55 +20558,55 @@
         <v>799</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="G6" s="8" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>1190</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>1182</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>1172</v>
-      </c>
-      <c r="J6" s="8" t="s">
+      <c r="K6" s="8" t="s">
         <v>1191</v>
       </c>
-      <c r="K6" s="8" t="s">
+    </row>
+    <row r="7" spans="1:11" ht="39.6" customHeight="1">
+      <c r="A7" s="8" t="s">
         <v>1192</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="B7" s="8" t="s">
+        <v>844</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>1193</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>845</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>1194</v>
       </c>
       <c r="D7" s="8">
         <v>2025</v>
       </c>
       <c r="E7" s="8" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>1195</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>1196</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>1197</v>
       </c>
-      <c r="I7" s="8" t="s">
-        <v>1172</v>
-      </c>
-      <c r="J7" s="8" t="s">
+      <c r="K7" s="8" t="s">
         <v>1198</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>1199</v>
       </c>
     </row>
   </sheetData>
@@ -20617,7 +20620,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
@@ -20631,9 +20634,9 @@
     <col min="14" max="14" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="7" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>767</v>
@@ -20645,39 +20648,39 @@
         <v>2</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>1202</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>1203</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>1204</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>1205</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>1206</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>1207</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>1208</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>787</v>
       </c>
       <c r="N1" s="7" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="8" t="s">
         <v>1209</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>1210</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -20694,7 +20697,7 @@
       <c r="K2" s="8"/>
       <c r="L2" s="8"/>
       <c r="M2" s="8" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="N2" s="8"/>
     </row>
@@ -20722,7 +20725,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="11.21875" customWidth="1"/>
@@ -20730,88 +20733,88 @@
     <col min="4" max="4" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="6" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1212</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>1213</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="6" t="s">
         <v>1214</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B2" t="s">
         <v>799</v>
       </c>
       <c r="C2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>811</v>
-      </c>
       <c r="B3" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="C3" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D3" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>869</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1194</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D4" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>853</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>870</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D4" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>854</v>
-      </c>
       <c r="C5" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>1216</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>1217</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
   </sheetData>
@@ -20822,115 +20825,115 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>1219</v>
       </c>
-      <c r="B1" s="7" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="57.6" customHeight="1">
+      <c r="A2" s="8" t="s">
         <v>1220</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="B2" s="8" t="s">
         <v>1221</v>
       </c>
-      <c r="B2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="8" t="s">
         <v>1222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>1223</v>
       </c>
       <c r="B3" s="8">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" s="8" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B4" s="8">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="86.4" customHeight="1">
       <c r="A5" s="8" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>1225</v>
       </c>
-      <c r="B5" s="8" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="57.6" customHeight="1">
+      <c r="A6" s="8" t="s">
         <v>1226</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="57.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="B6" s="8" t="s">
         <v>1227</v>
       </c>
-      <c r="B6" s="8" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="72" customHeight="1">
+      <c r="A7" s="8" t="s">
         <v>1228</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="B7" s="8" t="s">
         <v>1229</v>
       </c>
-      <c r="B7" s="8" t="s">
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="13" t="s">
         <v>1230</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="B10" s="13" t="s">
         <v>1231</v>
       </c>
-      <c r="B10" s="13" t="s">
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="8" t="s">
         <v>1232</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>1233</v>
       </c>
       <c r="B11" s="8">
         <f>COUNTIF(NISR_Source_Mapping!Y2:Y41,"Ready")</f>
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2">
       <c r="A12" s="8" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B12" s="8">
         <f>COUNTIF(NISR_Source_Mapping!Y2:Y41,"Needs Review")</f>
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2">
       <c r="A13" s="8" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B13" s="8">
         <f>COUNTIF(NISR_Source_Mapping!Y2:Y41,"Proxy—Approval Required")</f>
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2">
       <c r="A14" s="8" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B14" s="8">
         <f>COUNTIF(NISR_Source_Mapping!Y2:Y41,"To Map")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2">
       <c r="A15" s="8" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B15" s="8">
         <f>COUNTIF(Proposed_Updates!M2:M1000,"Approved")</f>
@@ -20948,207 +20951,207 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4">
       <c r="A1" s="14" t="s">
         <v>767</v>
       </c>
       <c r="B1" s="14" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>1238</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="14" t="s">
         <v>1239</v>
       </c>
-      <c r="D1" s="14" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="43.2">
+      <c r="A2" s="8" t="s">
+        <v>817</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>1240</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
-        <v>818</v>
-      </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="8" t="s">
         <v>1241</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="8" t="s">
         <v>1242</v>
       </c>
-      <c r="D2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="8" t="s">
+        <v>841</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>1243</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>842</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="8" t="s">
         <v>1244</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="D3" s="8" t="s">
         <v>1245</v>
       </c>
-      <c r="D3" s="8" t="s">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="8" t="s">
+        <v>899</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>1246</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>900</v>
-      </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" s="8" t="s">
         <v>1247</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="D4" s="8" t="s">
         <v>1248</v>
       </c>
-      <c r="D4" s="8" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="28.8">
+      <c r="A5" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>1249</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>922</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="C5" s="8" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>1250</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D5" s="8" t="s">
+    </row>
+    <row r="6" spans="1:4" ht="28.8">
+      <c r="A6" s="8" t="s">
+        <v>930</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>1251</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
-        <v>931</v>
-      </c>
-      <c r="B6" s="8" t="s">
+      <c r="C6" s="8" t="s">
         <v>1252</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="8" t="s">
         <v>1253</v>
       </c>
-      <c r="D6" s="8" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="28.8">
+      <c r="A7" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="B7" s="8" t="s">
         <v>1254</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>971</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="C7" s="8" t="s">
         <v>1255</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>1256</v>
       </c>
-      <c r="D7" s="8" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="28.8">
+      <c r="A8" s="8" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>1257</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B8" s="8" t="s">
+      <c r="C8" s="8" t="s">
         <v>1258</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="8" t="s">
         <v>1259</v>
       </c>
-      <c r="D8" s="8" t="s">
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="8" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>1260</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="C9" s="8" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>1261</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>1248</v>
-      </c>
-      <c r="D9" s="8" t="s">
+    </row>
+    <row r="10" spans="1:4" ht="28.8">
+      <c r="A10" s="8" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>1262</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B10" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>1263</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="8" t="s">
         <v>1264</v>
       </c>
-      <c r="D10" s="8" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="28.8">
+      <c r="A11" s="8" t="s">
         <v>1265</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
+      <c r="B11" s="8" t="s">
         <v>1266</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="8" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>1267</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D11" s="8" t="s">
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="8" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>1268</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
-        <v>1116</v>
-      </c>
-      <c r="B12" s="8" t="s">
+      <c r="C12" s="8" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D12" s="8" t="s">
         <v>1269</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>1245</v>
-      </c>
-      <c r="D12" s="8" t="s">
+    </row>
+    <row r="13" spans="1:4" ht="28.8">
+      <c r="A13" s="8" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>1270</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
-        <v>1136</v>
-      </c>
-      <c r="B13" s="8" t="s">
+      <c r="C13" s="8" t="s">
+        <v>1247</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>1271</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>1248</v>
-      </c>
-      <c r="D13" s="8" t="s">
+    </row>
+    <row r="14" spans="1:4" ht="28.8">
+      <c r="A14" s="8" t="s">
         <v>1272</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
+      <c r="B14" s="8" t="s">
         <v>1273</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="C14" s="8" t="s">
         <v>1274</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" s="8" t="s">
         <v>1275</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>1276</v>
       </c>
     </row>
   </sheetData>
